--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.26447322618898</v>
+        <v>13.20547689925571</v>
       </c>
       <c r="D2" t="n">
-        <v>81.34546105847767</v>
+        <v>13.21863742200262</v>
       </c>
       <c r="E2" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F2" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.65625240916793</v>
+        <v>4.006641016489789</v>
       </c>
       <c r="D3" t="n">
-        <v>15.69887507067656</v>
+        <v>2.551067198984942</v>
       </c>
       <c r="E3" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F3" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.43161300162267</v>
+        <v>9.170137112763683</v>
       </c>
       <c r="D4" t="n">
-        <v>60.44056797034344</v>
+        <v>9.821592295180809</v>
       </c>
       <c r="E4" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F4" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.1487691087016</v>
+        <v>2.13667498016401</v>
       </c>
       <c r="D5" t="n">
-        <v>4.500990422012882</v>
+        <v>0.7314109435770934</v>
       </c>
       <c r="E5" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F5" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.81517739965751</v>
+        <v>11.50746632744435</v>
       </c>
       <c r="D6" t="n">
-        <v>72.74016138606144</v>
+        <v>11.82027622523499</v>
       </c>
       <c r="E6" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F6" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.64651405952835</v>
+        <v>3.680058534673357</v>
       </c>
       <c r="D7" t="n">
-        <v>25.41525593079436</v>
+        <v>4.129979088754084</v>
       </c>
       <c r="E7" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F7" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.27668863458189</v>
+        <v>6.219961903119558</v>
       </c>
       <c r="D8" t="n">
-        <v>40.74281254677742</v>
+        <v>6.62070703885133</v>
       </c>
       <c r="E8" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F8" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.69722246474704</v>
+        <v>1.738298650521394</v>
       </c>
       <c r="D9" t="n">
-        <v>9.990600841779532</v>
+        <v>1.623472636789174</v>
       </c>
       <c r="E9" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F9" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.25018125779728</v>
+        <v>3.128154454392059</v>
       </c>
       <c r="D10" t="n">
-        <v>12.21520000291076</v>
+        <v>1.984970000472999</v>
       </c>
       <c r="E10" t="n">
-        <v>24.52718128352972</v>
+        <v>3.98566695857358</v>
       </c>
       <c r="F10" t="n">
-        <v>27.45574124313238</v>
+        <v>4.461557952009012</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
